--- a/fixtures/ficticios/siddex/articulos.xlsx
+++ b/fixtures/ficticios/siddex/articulos.xlsx
@@ -706,7 +706,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>134.000.842</t>
+          <t>900.000.842</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I33.000.786</t>
+          <t>Z33.000.786</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MO01001</t>
+          <t>SV09001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SERVICIO TURISMO (CONTRATOS)</t>
+          <t>SERVICIO FICTICIO (CONTRATOS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
